--- a/reports/schedule_report.xlsx
+++ b/reports/schedule_report.xlsx
@@ -16,12 +16,12 @@
     <sheet name="疑似误抓取" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'日程总览'!$A$1:$P$43</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'日程总览'!$A$1:$P$44</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'比赛时间优先'!$A$1:$P$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'报名截止提醒'!$A$1:$P$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'报名截止提醒'!$A$1:$P$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'结果公布提醒'!$A$1:$P$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'可进日历'!$A$1:$P$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'待核实'!$A$1:$P$32</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'可进日历'!$A$1:$P$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'待核实'!$A$1:$P$33</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'疑似误抓取'!$A$1:$P$16</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -442,7 +442,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P43"/>
+  <dimension ref="A1:P44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -3500,23 +3500,23 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>报名/报名截止</t>
+          <t>正式比赛</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr"/>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>周期性/待核实</t>
+          <t>疑似误提取</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>以年度通知为准</t>
+          <t>2009-20</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>挑战杯中国大学生创业计划竞赛</t>
+          <t>挑战杯丨第十五届“挑战杯”新疆维吾尔自治区大学生创业计划竞赛圆满落幕</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
@@ -3551,19 +3551,19 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>24</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
+          <t>https://www.tiaozhanbei.net/article/15858/</t>
+        </is>
+      </c>
+      <c r="N40" s="2" t="inlineStr">
+        <is>
           <t>https://www.tiaozhanbei.net/</t>
         </is>
       </c>
-      <c r="N40" s="2" t="inlineStr">
-        <is>
-          <t>https://www.tiaozhanbei.net/</t>
-        </is>
-      </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
           <t>否</t>
@@ -3571,14 +3571,14 @@
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>时间为周期性描述或需回源确认。</t>
+          <t>日期数值超出有效范围。</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>结果公布/获奖公示</t>
+          <t>报名/报名截止</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr"/>
@@ -3656,7 +3656,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>正式比赛</t>
+          <t>结果公布/获奖公示</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr"/>
@@ -3667,12 +3667,12 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>6月1日</t>
+          <t>以年度通知为准</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>竞赛章程（大挑）</t>
+          <t>挑战杯中国大学生创业计划竞赛</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
@@ -3707,12 +3707,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>40</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>https://www.tiaozhanbei.net/rules</t>
+          <t>https://www.tiaozhanbei.net/</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -3722,12 +3722,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>标题疑似导航/资讯/培训内容：章程。</t>
+          <t>时间为周期性描述或需回源确认。</t>
         </is>
       </c>
     </row>
@@ -3750,67 +3750,145 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
+          <t>竞赛章程（大挑）</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>创新创业类</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>P3 低优先级</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="K43" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="L43" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="inlineStr">
+        <is>
+          <t>https://www.tiaozhanbei.net/rules</t>
+        </is>
+      </c>
+      <c r="N43" s="2" t="inlineStr">
+        <is>
+          <t>https://www.tiaozhanbei.net/</t>
+        </is>
+      </c>
+      <c r="O43" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="P43" s="2" t="inlineStr">
+        <is>
+          <t>标题疑似导航/资讯/培训内容：章程。</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>正式比赛</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr"/>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>周期性/待核实</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>6月1日</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
           <t>竞赛章程（小挑）</t>
         </is>
       </c>
-      <c r="F43" s="2" t="inlineStr">
+      <c r="F44" s="2" t="inlineStr">
         <is>
           <t>创新创业类</t>
         </is>
       </c>
-      <c r="G43" s="2" t="inlineStr">
+      <c r="G44" s="2" t="inlineStr">
         <is>
           <t>P3 低优先级</t>
         </is>
       </c>
-      <c r="H43" s="2" t="inlineStr">
+      <c r="H44" s="2" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="I43" s="2" t="inlineStr">
+      <c r="I44" s="2" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="J43" s="2" t="inlineStr">
+      <c r="J44" s="2" t="inlineStr">
         <is>
           <t>64</t>
         </is>
       </c>
-      <c r="K43" s="2" t="inlineStr">
+      <c r="K44" s="2" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="L43" s="2" t="inlineStr">
+      <c r="L44" s="2" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="M43" s="2" t="inlineStr">
+      <c r="M44" s="2" t="inlineStr">
         <is>
           <t>https://www.tiaozhanbei.net/rules2</t>
         </is>
       </c>
-      <c r="N43" s="2" t="inlineStr">
+      <c r="N44" s="2" t="inlineStr">
         <is>
           <t>https://www.tiaozhanbei.net/</t>
         </is>
       </c>
-      <c r="O43" s="2" t="inlineStr">
+      <c r="O44" s="2" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="P43" s="2" t="inlineStr">
+      <c r="P44" s="2" t="inlineStr">
         <is>
           <t>标题疑似导航/资讯/培训内容：章程。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:P43"/>
+  <autoFilter ref="A1:P44"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3936,14 +4014,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P2"/>
+  <dimension ref="A1:P1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
@@ -3951,8 +4029,8 @@
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="35" customWidth="1" min="13" max="13"/>
-    <col width="35" customWidth="1" min="14" max="14"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
   </cols>
@@ -4039,86 +4117,8 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>报名/报名截止</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>具体日期</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>2026年9月10日</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>全国大学生数学建模竞赛</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>数学建模类</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>P1 优先关注</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="I2" s="2" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
-      <c r="J2" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="K2" s="2" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="L2" s="2" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
-      <c r="M2" s="2" t="inlineStr">
-        <is>
-          <t>https://www.mcm.edu.cn/index.moma</t>
-        </is>
-      </c>
-      <c r="N2" s="2" t="inlineStr">
-        <is>
-          <t>https://www.mcm.edu.cn/index.moma</t>
-        </is>
-      </c>
-      <c r="O2" s="2" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="P2" s="2" t="inlineStr"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:P2"/>
+  <autoFilter ref="A1:P1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4244,14 +4244,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P2"/>
+  <dimension ref="A1:P1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
@@ -4259,8 +4259,8 @@
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="35" customWidth="1" min="13" max="13"/>
-    <col width="35" customWidth="1" min="14" max="14"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
   </cols>
@@ -4347,86 +4347,8 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>报名/报名截止</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>具体日期</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>2026年9月10日</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>全国大学生数学建模竞赛</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>数学建模类</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>P1 优先关注</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="I2" s="2" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
-      <c r="J2" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="K2" s="2" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="L2" s="2" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
-      <c r="M2" s="2" t="inlineStr">
-        <is>
-          <t>https://www.mcm.edu.cn/index.moma</t>
-        </is>
-      </c>
-      <c r="N2" s="2" t="inlineStr">
-        <is>
-          <t>https://www.mcm.edu.cn/index.moma</t>
-        </is>
-      </c>
-      <c r="O2" s="2" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="P2" s="2" t="inlineStr"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:P2"/>
+  <autoFilter ref="A1:P1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4437,14 +4359,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P32"/>
+  <dimension ref="A1:P33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
-    <col width="34" customWidth="1" min="5" max="5"/>
+    <col width="36" customWidth="1" min="5" max="5"/>
     <col width="27" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
@@ -6781,23 +6703,23 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>报名/报名截止</t>
+          <t>正式比赛</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr"/>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>周期性/待核实</t>
+          <t>疑似误提取</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>以年度通知为准</t>
+          <t>2009-20</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>挑战杯中国大学生创业计划竞赛</t>
+          <t>挑战杯丨第十五届“挑战杯”新疆维吾尔自治区大学生创业计划竞赛圆满落幕</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
@@ -6832,19 +6754,19 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>24</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
+          <t>https://www.tiaozhanbei.net/article/15858/</t>
+        </is>
+      </c>
+      <c r="N31" s="2" t="inlineStr">
+        <is>
           <t>https://www.tiaozhanbei.net/</t>
         </is>
       </c>
-      <c r="N31" s="2" t="inlineStr">
-        <is>
-          <t>https://www.tiaozhanbei.net/</t>
-        </is>
-      </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
           <t>否</t>
@@ -6852,14 +6774,14 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>时间为周期性描述或需回源确认。</t>
+          <t>日期数值超出有效范围。</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>结果公布/获奖公示</t>
+          <t>报名/报名截止</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr"/>
@@ -6934,8 +6856,86 @@
         </is>
       </c>
     </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>结果公布/获奖公示</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr"/>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>周期性/待核实</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>以年度通知为准</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>挑战杯中国大学生创业计划竞赛</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>创新创业类</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>P3 低优先级</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="K33" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="L33" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr">
+        <is>
+          <t>https://www.tiaozhanbei.net/</t>
+        </is>
+      </c>
+      <c r="N33" s="2" t="inlineStr">
+        <is>
+          <t>https://www.tiaozhanbei.net/</t>
+        </is>
+      </c>
+      <c r="O33" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="P33" s="2" t="inlineStr">
+        <is>
+          <t>时间为周期性描述或需回源确认。</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:P32"/>
+  <autoFilter ref="A1:P33"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/reports/schedule_report.xlsx
+++ b/reports/schedule_report.xlsx
@@ -16,13 +16,13 @@
     <sheet name="疑似误抓取" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'日程总览'!$A$1:$P$44</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'日程总览'!$A$1:$P$43</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'比赛时间优先'!$A$1:$P$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'报名截止提醒'!$A$1:$P$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'结果公布提醒'!$A$1:$P$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'可进日历'!$A$1:$P$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'待核实'!$A$1:$P$33</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'疑似误抓取'!$A$1:$P$16</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'待核实'!$A$1:$P$32</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'疑似误抓取'!$A$1:$P$17</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -442,7 +442,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P44"/>
+  <dimension ref="A1:P43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -3500,23 +3500,23 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>正式比赛</t>
+          <t>报名/报名截止</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr"/>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>疑似误提取</t>
+          <t>周期性/待核实</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>2009-20</t>
+          <t>以年度通知为准</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>挑战杯丨第十五届“挑战杯”新疆维吾尔自治区大学生创业计划竞赛圆满落幕</t>
+          <t>挑战杯中国大学生创业计划竞赛</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>40</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>https://www.tiaozhanbei.net/article/15858/</t>
+          <t>https://www.tiaozhanbei.net/</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -3571,14 +3571,14 @@
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>日期数值超出有效范围。</t>
+          <t>时间为周期性描述或需回源确认。</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>报名/报名截止</t>
+          <t>结果公布/获奖公示</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr"/>
@@ -3656,7 +3656,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>结果公布/获奖公示</t>
+          <t>正式比赛</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr"/>
@@ -3667,12 +3667,12 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>以年度通知为准</t>
+          <t>6月1日</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>挑战杯中国大学生创业计划竞赛</t>
+          <t>竞赛章程（大挑）</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
@@ -3707,27 +3707,27 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>24</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
+          <t>https://www.tiaozhanbei.net/rules</t>
+        </is>
+      </c>
+      <c r="N42" s="2" t="inlineStr">
+        <is>
           <t>https://www.tiaozhanbei.net/</t>
         </is>
       </c>
-      <c r="N42" s="2" t="inlineStr">
-        <is>
-          <t>https://www.tiaozhanbei.net/</t>
-        </is>
-      </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>时间为周期性描述或需回源确认。</t>
+          <t>标题疑似导航/资讯/培训内容：章程。</t>
         </is>
       </c>
     </row>
@@ -3750,7 +3750,7 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>竞赛章程（大挑）</t>
+          <t>竞赛章程（小挑）</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
@@ -3790,7 +3790,7 @@
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>https://www.tiaozhanbei.net/rules</t>
+          <t>https://www.tiaozhanbei.net/rules2</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -3809,86 +3809,8 @@
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="2" t="inlineStr">
-        <is>
-          <t>正式比赛</t>
-        </is>
-      </c>
-      <c r="B44" s="2" t="inlineStr"/>
-      <c r="C44" s="2" t="inlineStr">
-        <is>
-          <t>周期性/待核实</t>
-        </is>
-      </c>
-      <c r="D44" s="2" t="inlineStr">
-        <is>
-          <t>6月1日</t>
-        </is>
-      </c>
-      <c r="E44" s="2" t="inlineStr">
-        <is>
-          <t>竞赛章程（小挑）</t>
-        </is>
-      </c>
-      <c r="F44" s="2" t="inlineStr">
-        <is>
-          <t>创新创业类</t>
-        </is>
-      </c>
-      <c r="G44" s="2" t="inlineStr">
-        <is>
-          <t>P3 低优先级</t>
-        </is>
-      </c>
-      <c r="H44" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="I44" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="J44" s="2" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="K44" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="L44" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="M44" s="2" t="inlineStr">
-        <is>
-          <t>https://www.tiaozhanbei.net/rules2</t>
-        </is>
-      </c>
-      <c r="N44" s="2" t="inlineStr">
-        <is>
-          <t>https://www.tiaozhanbei.net/</t>
-        </is>
-      </c>
-      <c r="O44" s="2" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="P44" s="2" t="inlineStr">
-        <is>
-          <t>标题疑似导航/资讯/培训内容：章程。</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:P44"/>
+  <autoFilter ref="A1:P43"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4359,14 +4281,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P33"/>
+  <dimension ref="A1:P32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
-    <col width="36" customWidth="1" min="5" max="5"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
     <col width="27" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
@@ -6703,23 +6625,23 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>正式比赛</t>
+          <t>报名/报名截止</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr"/>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>疑似误提取</t>
+          <t>周期性/待核实</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>2009-20</t>
+          <t>以年度通知为准</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>挑战杯丨第十五届“挑战杯”新疆维吾尔自治区大学生创业计划竞赛圆满落幕</t>
+          <t>挑战杯中国大学生创业计划竞赛</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
@@ -6754,12 +6676,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>40</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>https://www.tiaozhanbei.net/article/15858/</t>
+          <t>https://www.tiaozhanbei.net/</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -6774,14 +6696,14 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>日期数值超出有效范围。</t>
+          <t>时间为周期性描述或需回源确认。</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>报名/报名截止</t>
+          <t>结果公布/获奖公示</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr"/>
@@ -6856,86 +6778,8 @@
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>结果公布/获奖公示</t>
-        </is>
-      </c>
-      <c r="B33" s="2" t="inlineStr"/>
-      <c r="C33" s="2" t="inlineStr">
-        <is>
-          <t>周期性/待核实</t>
-        </is>
-      </c>
-      <c r="D33" s="2" t="inlineStr">
-        <is>
-          <t>以年度通知为准</t>
-        </is>
-      </c>
-      <c r="E33" s="2" t="inlineStr">
-        <is>
-          <t>挑战杯中国大学生创业计划竞赛</t>
-        </is>
-      </c>
-      <c r="F33" s="2" t="inlineStr">
-        <is>
-          <t>创新创业类</t>
-        </is>
-      </c>
-      <c r="G33" s="2" t="inlineStr">
-        <is>
-          <t>P3 低优先级</t>
-        </is>
-      </c>
-      <c r="H33" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="I33" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="J33" s="2" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="K33" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="L33" s="2" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="M33" s="2" t="inlineStr">
-        <is>
-          <t>https://www.tiaozhanbei.net/</t>
-        </is>
-      </c>
-      <c r="N33" s="2" t="inlineStr">
-        <is>
-          <t>https://www.tiaozhanbei.net/</t>
-        </is>
-      </c>
-      <c r="O33" s="2" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="P33" s="2" t="inlineStr">
-        <is>
-          <t>时间为周期性描述或需回源确认。</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:P33"/>
+  <autoFilter ref="A1:P32"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -6946,7 +6790,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P16"/>
+  <dimension ref="A1:P17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -7064,7 +6908,7 @@
       <c r="D2" s="2" t="inlineStr"/>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>SPSSPRO</t>
+          <t>2026年全国大学生数学建模竞赛赛题讲评与经验交流会通知</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -7104,7 +6948,7 @@
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>https://www.spsspro.com/?utm_source=cumcm</t>
+          <t>https://www.mcm.edu.cn/html_cn/node/74ca2bd675a8399782a41dffa15f0910.html</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
@@ -7119,7 +6963,7 @@
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>标题命中误抓取关键词：SPSSPRO。</t>
+          <t>标题疑似导航/资讯/培训内容：通知。</t>
         </is>
       </c>
     </row>
@@ -7138,7 +6982,7 @@
       <c r="D3" s="2" t="inlineStr"/>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>《数学建模及其应用》</t>
+          <t>SPSSPRO</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -7178,7 +7022,7 @@
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>http://qxyy.cbpt.cnki.net</t>
+          <t>https://www.spsspro.com/?utm_source=cumcm</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
@@ -7193,7 +7037,7 @@
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>标题命中误抓取关键词：《数学建模及其应用》。</t>
+          <t>标题命中误抓取关键词：SPSSPRO。</t>
         </is>
       </c>
     </row>
@@ -7209,14 +7053,10 @@
           <t>疑似误抓取</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>报名时间: 2026年9月10日</t>
-        </is>
-      </c>
+      <c r="D4" s="2" t="inlineStr"/>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>中国知网</t>
+          <t>《数学建模及其应用》</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -7256,7 +7096,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>http://cumcm.cnki.net</t>
+          <t>http://qxyy.cbpt.cnki.net</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7271,7 +7111,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>标题命中误抓取关键词：中国知网。</t>
+          <t>标题命中误抓取关键词：《数学建模及其应用》。</t>
         </is>
       </c>
     </row>
@@ -7287,10 +7127,14 @@
           <t>疑似误抓取</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr"/>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>报名时间: 2026年9月10日</t>
+        </is>
+      </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>中国高校数学建模课程中心</t>
+          <t>中国知网</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -7330,7 +7174,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>http://cumcm.icourses.cn/</t>
+          <t>http://cumcm.cnki.net</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7345,7 +7189,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>标题疑似导航/资讯/培训内容：课程中心。</t>
+          <t>标题命中误抓取关键词：中国知网。</t>
         </is>
       </c>
     </row>
@@ -7364,7 +7208,7 @@
       <c r="D6" s="2" t="inlineStr"/>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>竞赛组织</t>
+          <t>中国高校数学建模课程中心</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -7404,7 +7248,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>https://www.mcm.edu.cn/html_cn/section/302f2c2355b1179ada9b99a06d7109f5.html</t>
+          <t>http://cumcm.icourses.cn/</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -7419,7 +7263,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>标题命中误抓取关键词：竞赛组织。</t>
+          <t>标题疑似导航/资讯/培训内容：课程中心。</t>
         </is>
       </c>
     </row>
@@ -7438,7 +7282,7 @@
       <c r="D7" s="2" t="inlineStr"/>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>苏州同元软控信息技术有限公司</t>
+          <t>竞赛组织</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -7478,7 +7322,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>https://www.tongyuan.cc/?utm_source=cumcm</t>
+          <t>https://www.mcm.edu.cn/html_cn/section/302f2c2355b1179ada9b99a06d7109f5.html</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7493,7 +7337,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>标题命中误抓取关键词：苏州同元软控信息技术有限公司。</t>
+          <t>标题命中误抓取关键词：竞赛组织。</t>
         </is>
       </c>
     </row>
@@ -7512,12 +7356,12 @@
       <c r="D8" s="2" t="inlineStr"/>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>大数据和人工智能</t>
+          <t>苏州同元软控信息技术有限公司</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>数据分析 / 统计建模类</t>
+          <t>数学建模类</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7527,12 +7371,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>S</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>46</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7542,22 +7386,22 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>100</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>32</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>https://www.datafountain.cn/competitions/1153</t>
+          <t>https://www.tongyuan.cc/?utm_source=cumcm</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>https://www.datafountain.cn/competitions</t>
+          <t>https://www.mcm.edu.cn/index.moma</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
@@ -7567,7 +7411,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>标题是平台栏目或泛化主题，不是明确比赛名称。</t>
+          <t>标题命中误抓取关键词：苏州同元软控信息技术有限公司。</t>
         </is>
       </c>
     </row>
@@ -7586,7 +7430,7 @@
       <c r="D9" s="2" t="inlineStr"/>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>数据科学竞赛/大数据 Competitions - DataFountain</t>
+          <t>大数据和人工智能</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -7626,7 +7470,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>https://www.datafountain.cn/competitions</t>
+          <t>https://www.datafountain.cn/competitions/1153</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7660,17 +7504,17 @@
       <c r="D10" s="2" t="inlineStr"/>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>å ¨å½å¤§å­¦çè±è¯­ç«èµ-NECCS</t>
+          <t>数据科学竞赛/大数据 Competitions - DataFountain</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>英语与财经表达类</t>
+          <t>数据分析 / 统计建模类</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>P3 低优先级</t>
+          <t>P2 可选参加</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -7680,7 +7524,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>42</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7690,22 +7534,22 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>66</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>100</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>https://www.chinaneccs.cn/</t>
+          <t>https://www.datafountain.cn/competitions</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>https://www.chinaneccs.cn/</t>
+          <t>https://www.datafountain.cn/competitions</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
@@ -7715,7 +7559,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>标题疑似编码异常或乱码。</t>
+          <t>标题是平台栏目或泛化主题，不是明确比赛名称。</t>
         </is>
       </c>
     </row>
@@ -7734,12 +7578,12 @@
       <c r="D11" s="2" t="inlineStr"/>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>大赛通知</t>
+          <t>å ¨å½å¤§å­¦çè±è¯­ç«èµ-NECCS</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>创新创业类</t>
+          <t>英语与财经表达类</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7749,7 +7593,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -7759,7 +7603,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>22</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -7769,17 +7613,17 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>24</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>https://t3.chei.com.cn/ncss/cy/web/lib/dasaitongzhi-2026.zip</t>
+          <t>https://www.chinaneccs.cn/</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>https://cy.ncss.cn/</t>
+          <t>https://www.chinaneccs.cn/</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
@@ -7789,7 +7633,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>标题疑似导航/资讯/培训内容：通知。</t>
+          <t>标题疑似编码异常或乱码。</t>
         </is>
       </c>
     </row>
@@ -7805,14 +7649,10 @@
           <t>疑似误抓取</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>比赛时间: 2026.06.19</t>
-        </is>
-      </c>
+      <c r="D12" s="2" t="inlineStr"/>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>挑战杯 全国大学生课外学术科技作品竞赛和创业计划大赛 官方网站 移动版</t>
+          <t>大赛通知</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -7827,7 +7667,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>A</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -7847,17 +7687,17 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>40</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>https://www.tiaozhanbei.net/</t>
+          <t>https://t3.chei.com.cn/ncss/cy/web/lib/dasaitongzhi-2026.zip</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>https://www.tiaozhanbei.net/</t>
+          <t>https://cy.ncss.cn/</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
@@ -7867,7 +7707,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>标题命中误抓取关键词：官方网站 移动版。</t>
+          <t>标题疑似导航/资讯/培训内容：通知。</t>
         </is>
       </c>
     </row>
@@ -7890,7 +7730,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>挑战杯动态</t>
+          <t>挑战杯 全国大学生课外学术科技作品竞赛和创业计划大赛 官方网站 移动版</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -7905,7 +7745,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>S</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -7930,7 +7770,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>https://www.tiaozhanbei.net/tzb</t>
+          <t>https://www.tiaozhanbei.net/</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7945,7 +7785,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>标题疑似导航/资讯/培训内容：动态。</t>
+          <t>标题命中误抓取关键词：官方网站 移动版。</t>
         </is>
       </c>
     </row>
@@ -7963,12 +7803,12 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>比赛时间: 6月1日</t>
+          <t>比赛时间: 2026.06.19</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>竞赛章程（大挑）</t>
+          <t>挑战杯动态</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -8008,7 +7848,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>https://www.tiaozhanbei.net/rules</t>
+          <t>https://www.tiaozhanbei.net/tzb</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8023,7 +7863,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>标题疑似导航/资讯/培训内容：章程。</t>
+          <t>标题疑似导航/资讯/培训内容：动态。</t>
         </is>
       </c>
     </row>
@@ -8046,7 +7886,7 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>竞赛章程（小挑）</t>
+          <t>竞赛章程（大挑）</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -8086,7 +7926,7 @@
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>https://www.tiaozhanbei.net/rules2</t>
+          <t>https://www.tiaozhanbei.net/rules</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -8117,70 +7957,148 @@
           <t>疑似误抓取</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr"/>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>比赛时间: 6月1日</t>
+        </is>
+      </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
+          <t>竞赛章程（小挑）</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>创新创业类</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>P3 低优先级</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>https://www.tiaozhanbei.net/rules2</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>https://www.tiaozhanbei.net/</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>标题疑似导航/资讯/培训内容：章程。</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>疑似误抓取</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr"/>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>疑似误抓取</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr"/>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
           <t>竞赛简介</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="F17" s="2" t="inlineStr">
         <is>
           <t>创新创业类</t>
         </is>
       </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="G17" s="2" t="inlineStr">
         <is>
           <t>P3 低优先级</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
+      <c r="I17" s="2" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="J16" s="2" t="inlineStr">
+      <c r="J17" s="2" t="inlineStr">
         <is>
           <t>64</t>
         </is>
       </c>
-      <c r="K16" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="L16" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="M16" s="2" t="inlineStr">
+      <c r="M17" s="2" t="inlineStr">
         <is>
           <t>https://www.tiaozhanbei.net/focus</t>
         </is>
       </c>
-      <c r="N16" s="2" t="inlineStr">
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>https://www.tiaozhanbei.net/</t>
         </is>
       </c>
-      <c r="O16" s="2" t="inlineStr">
+      <c r="O17" s="2" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="P16" s="2" t="inlineStr">
+      <c r="P17" s="2" t="inlineStr">
         <is>
           <t>标题疑似导航/资讯/培训内容：简介。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:P16"/>
+  <autoFilter ref="A1:P17"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/reports/schedule_report.xlsx
+++ b/reports/schedule_report.xlsx
@@ -16,12 +16,12 @@
     <sheet name="疑似误抓取" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'日程总览'!$A$1:$P$43</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'日程总览'!$A$1:$P$44</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'比赛时间优先'!$A$1:$P$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'报名截止提醒'!$A$1:$P$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'结果公布提醒'!$A$1:$P$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'可进日历'!$A$1:$P$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'待核实'!$A$1:$P$32</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'待核实'!$A$1:$P$33</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'疑似误抓取'!$A$1:$P$17</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -442,7 +442,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P43"/>
+  <dimension ref="A1:P44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -3500,23 +3500,23 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>报名/报名截止</t>
+          <t>正式比赛</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr"/>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>周期性/待核实</t>
+          <t>疑似误提取</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>以年度通知为准</t>
+          <t>2009-20</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>挑战杯中国大学生创业计划竞赛</t>
+          <t>挑战杯丨第十五届“挑战杯”新疆维吾尔自治区大学生创业计划竞赛圆满落幕</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
@@ -3551,19 +3551,19 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>24</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
+          <t>https://www.tiaozhanbei.net/article/15858/</t>
+        </is>
+      </c>
+      <c r="N40" s="2" t="inlineStr">
+        <is>
           <t>https://www.tiaozhanbei.net/</t>
         </is>
       </c>
-      <c r="N40" s="2" t="inlineStr">
-        <is>
-          <t>https://www.tiaozhanbei.net/</t>
-        </is>
-      </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
           <t>否</t>
@@ -3571,14 +3571,14 @@
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>时间为周期性描述或需回源确认。</t>
+          <t>日期数值超出有效范围。</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>结果公布/获奖公示</t>
+          <t>报名/报名截止</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr"/>
@@ -3656,7 +3656,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>正式比赛</t>
+          <t>结果公布/获奖公示</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr"/>
@@ -3667,12 +3667,12 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>6月1日</t>
+          <t>以年度通知为准</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>竞赛章程（大挑）</t>
+          <t>挑战杯中国大学生创业计划竞赛</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
@@ -3707,12 +3707,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>40</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>https://www.tiaozhanbei.net/rules</t>
+          <t>https://www.tiaozhanbei.net/</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -3722,12 +3722,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>标题疑似导航/资讯/培训内容：章程。</t>
+          <t>时间为周期性描述或需回源确认。</t>
         </is>
       </c>
     </row>
@@ -3750,67 +3750,145 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
+          <t>竞赛章程（大挑）</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>创新创业类</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>P3 低优先级</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="K43" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="L43" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="inlineStr">
+        <is>
+          <t>https://www.tiaozhanbei.net/rules</t>
+        </is>
+      </c>
+      <c r="N43" s="2" t="inlineStr">
+        <is>
+          <t>https://www.tiaozhanbei.net/</t>
+        </is>
+      </c>
+      <c r="O43" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="P43" s="2" t="inlineStr">
+        <is>
+          <t>标题疑似导航/资讯/培训内容：章程。</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>正式比赛</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr"/>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>周期性/待核实</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>6月1日</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
           <t>竞赛章程（小挑）</t>
         </is>
       </c>
-      <c r="F43" s="2" t="inlineStr">
+      <c r="F44" s="2" t="inlineStr">
         <is>
           <t>创新创业类</t>
         </is>
       </c>
-      <c r="G43" s="2" t="inlineStr">
+      <c r="G44" s="2" t="inlineStr">
         <is>
           <t>P3 低优先级</t>
         </is>
       </c>
-      <c r="H43" s="2" t="inlineStr">
+      <c r="H44" s="2" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="I43" s="2" t="inlineStr">
+      <c r="I44" s="2" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="J43" s="2" t="inlineStr">
+      <c r="J44" s="2" t="inlineStr">
         <is>
           <t>64</t>
         </is>
       </c>
-      <c r="K43" s="2" t="inlineStr">
+      <c r="K44" s="2" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="L43" s="2" t="inlineStr">
+      <c r="L44" s="2" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="M43" s="2" t="inlineStr">
+      <c r="M44" s="2" t="inlineStr">
         <is>
           <t>https://www.tiaozhanbei.net/rules2</t>
         </is>
       </c>
-      <c r="N43" s="2" t="inlineStr">
+      <c r="N44" s="2" t="inlineStr">
         <is>
           <t>https://www.tiaozhanbei.net/</t>
         </is>
       </c>
-      <c r="O43" s="2" t="inlineStr">
+      <c r="O44" s="2" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="P43" s="2" t="inlineStr">
+      <c r="P44" s="2" t="inlineStr">
         <is>
           <t>标题疑似导航/资讯/培训内容：章程。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:P43"/>
+  <autoFilter ref="A1:P44"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4281,14 +4359,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P32"/>
+  <dimension ref="A1:P33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
-    <col width="34" customWidth="1" min="5" max="5"/>
+    <col width="36" customWidth="1" min="5" max="5"/>
     <col width="27" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
@@ -6625,23 +6703,23 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>报名/报名截止</t>
+          <t>正式比赛</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr"/>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>周期性/待核实</t>
+          <t>疑似误提取</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>以年度通知为准</t>
+          <t>2009-20</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>挑战杯中国大学生创业计划竞赛</t>
+          <t>挑战杯丨第十五届“挑战杯”新疆维吾尔自治区大学生创业计划竞赛圆满落幕</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
@@ -6676,19 +6754,19 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>24</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
+          <t>https://www.tiaozhanbei.net/article/15858/</t>
+        </is>
+      </c>
+      <c r="N31" s="2" t="inlineStr">
+        <is>
           <t>https://www.tiaozhanbei.net/</t>
         </is>
       </c>
-      <c r="N31" s="2" t="inlineStr">
-        <is>
-          <t>https://www.tiaozhanbei.net/</t>
-        </is>
-      </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
           <t>否</t>
@@ -6696,14 +6774,14 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>时间为周期性描述或需回源确认。</t>
+          <t>日期数值超出有效范围。</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>结果公布/获奖公示</t>
+          <t>报名/报名截止</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr"/>
@@ -6778,8 +6856,86 @@
         </is>
       </c>
     </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>结果公布/获奖公示</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr"/>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>周期性/待核实</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>以年度通知为准</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>挑战杯中国大学生创业计划竞赛</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>创新创业类</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>P3 低优先级</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="K33" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="L33" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr">
+        <is>
+          <t>https://www.tiaozhanbei.net/</t>
+        </is>
+      </c>
+      <c r="N33" s="2" t="inlineStr">
+        <is>
+          <t>https://www.tiaozhanbei.net/</t>
+        </is>
+      </c>
+      <c r="O33" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="P33" s="2" t="inlineStr">
+        <is>
+          <t>时间为周期性描述或需回源确认。</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:P32"/>
+  <autoFilter ref="A1:P33"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/reports/schedule_report.xlsx
+++ b/reports/schedule_report.xlsx
@@ -16,12 +16,12 @@
     <sheet name="疑似误抓取" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'日程总览'!$A$1:$P$44</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'日程总览'!$A$1:$P$43</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'比赛时间优先'!$A$1:$P$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'报名截止提醒'!$A$1:$P$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'结果公布提醒'!$A$1:$P$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'可进日历'!$A$1:$P$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'待核实'!$A$1:$P$33</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'待核实'!$A$1:$P$32</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'疑似误抓取'!$A$1:$P$17</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -442,7 +442,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P44"/>
+  <dimension ref="A1:P43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -3500,23 +3500,23 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>正式比赛</t>
+          <t>报名/报名截止</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr"/>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>疑似误提取</t>
+          <t>周期性/待核实</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>2009-20</t>
+          <t>以年度通知为准</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>挑战杯丨第十五届“挑战杯”新疆维吾尔自治区大学生创业计划竞赛圆满落幕</t>
+          <t>挑战杯中国大学生创业计划竞赛</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>40</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>https://www.tiaozhanbei.net/article/15858/</t>
+          <t>https://www.tiaozhanbei.net/</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -3571,14 +3571,14 @@
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>日期数值超出有效范围。</t>
+          <t>时间为周期性描述或需回源确认。</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>报名/报名截止</t>
+          <t>结果公布/获奖公示</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr"/>
@@ -3656,7 +3656,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>结果公布/获奖公示</t>
+          <t>正式比赛</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr"/>
@@ -3667,12 +3667,12 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>以年度通知为准</t>
+          <t>6月1日</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>挑战杯中国大学生创业计划竞赛</t>
+          <t>竞赛章程（大挑）</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
@@ -3707,27 +3707,27 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>24</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
+          <t>https://www.tiaozhanbei.net/rules</t>
+        </is>
+      </c>
+      <c r="N42" s="2" t="inlineStr">
+        <is>
           <t>https://www.tiaozhanbei.net/</t>
         </is>
       </c>
-      <c r="N42" s="2" t="inlineStr">
-        <is>
-          <t>https://www.tiaozhanbei.net/</t>
-        </is>
-      </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>时间为周期性描述或需回源确认。</t>
+          <t>标题疑似导航/资讯/培训内容：章程。</t>
         </is>
       </c>
     </row>
@@ -3750,7 +3750,7 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>竞赛章程（大挑）</t>
+          <t>竞赛章程（小挑）</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
@@ -3790,7 +3790,7 @@
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>https://www.tiaozhanbei.net/rules</t>
+          <t>https://www.tiaozhanbei.net/rules2</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -3809,86 +3809,8 @@
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="2" t="inlineStr">
-        <is>
-          <t>正式比赛</t>
-        </is>
-      </c>
-      <c r="B44" s="2" t="inlineStr"/>
-      <c r="C44" s="2" t="inlineStr">
-        <is>
-          <t>周期性/待核实</t>
-        </is>
-      </c>
-      <c r="D44" s="2" t="inlineStr">
-        <is>
-          <t>6月1日</t>
-        </is>
-      </c>
-      <c r="E44" s="2" t="inlineStr">
-        <is>
-          <t>竞赛章程（小挑）</t>
-        </is>
-      </c>
-      <c r="F44" s="2" t="inlineStr">
-        <is>
-          <t>创新创业类</t>
-        </is>
-      </c>
-      <c r="G44" s="2" t="inlineStr">
-        <is>
-          <t>P3 低优先级</t>
-        </is>
-      </c>
-      <c r="H44" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="I44" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="J44" s="2" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="K44" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="L44" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="M44" s="2" t="inlineStr">
-        <is>
-          <t>https://www.tiaozhanbei.net/rules2</t>
-        </is>
-      </c>
-      <c r="N44" s="2" t="inlineStr">
-        <is>
-          <t>https://www.tiaozhanbei.net/</t>
-        </is>
-      </c>
-      <c r="O44" s="2" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="P44" s="2" t="inlineStr">
-        <is>
-          <t>标题疑似导航/资讯/培训内容：章程。</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:P44"/>
+  <autoFilter ref="A1:P43"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4359,14 +4281,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P33"/>
+  <dimension ref="A1:P32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
-    <col width="36" customWidth="1" min="5" max="5"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
     <col width="27" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
@@ -6703,23 +6625,23 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>正式比赛</t>
+          <t>报名/报名截止</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr"/>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>疑似误提取</t>
+          <t>周期性/待核实</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>2009-20</t>
+          <t>以年度通知为准</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>挑战杯丨第十五届“挑战杯”新疆维吾尔自治区大学生创业计划竞赛圆满落幕</t>
+          <t>挑战杯中国大学生创业计划竞赛</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
@@ -6754,12 +6676,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>40</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>https://www.tiaozhanbei.net/article/15858/</t>
+          <t>https://www.tiaozhanbei.net/</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -6774,14 +6696,14 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>日期数值超出有效范围。</t>
+          <t>时间为周期性描述或需回源确认。</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>报名/报名截止</t>
+          <t>结果公布/获奖公示</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr"/>
@@ -6856,86 +6778,8 @@
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>结果公布/获奖公示</t>
-        </is>
-      </c>
-      <c r="B33" s="2" t="inlineStr"/>
-      <c r="C33" s="2" t="inlineStr">
-        <is>
-          <t>周期性/待核实</t>
-        </is>
-      </c>
-      <c r="D33" s="2" t="inlineStr">
-        <is>
-          <t>以年度通知为准</t>
-        </is>
-      </c>
-      <c r="E33" s="2" t="inlineStr">
-        <is>
-          <t>挑战杯中国大学生创业计划竞赛</t>
-        </is>
-      </c>
-      <c r="F33" s="2" t="inlineStr">
-        <is>
-          <t>创新创业类</t>
-        </is>
-      </c>
-      <c r="G33" s="2" t="inlineStr">
-        <is>
-          <t>P3 低优先级</t>
-        </is>
-      </c>
-      <c r="H33" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="I33" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="J33" s="2" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="K33" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="L33" s="2" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="M33" s="2" t="inlineStr">
-        <is>
-          <t>https://www.tiaozhanbei.net/</t>
-        </is>
-      </c>
-      <c r="N33" s="2" t="inlineStr">
-        <is>
-          <t>https://www.tiaozhanbei.net/</t>
-        </is>
-      </c>
-      <c r="O33" s="2" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="P33" s="2" t="inlineStr">
-        <is>
-          <t>时间为周期性描述或需回源确认。</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:P33"/>
+  <autoFilter ref="A1:P32"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/reports/schedule_report.xlsx
+++ b/reports/schedule_report.xlsx
@@ -1029,7 +1029,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -1039,22 +1039,22 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026年9月10日</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>中国国际大学生创新大赛</t>
+          <t>全国大学生数学建模竞赛</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>创新创业类</t>
+          <t>数学建模类</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>P2 可选参加</t>
+          <t>P1 优先关注</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -1064,32 +1064,32 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>46</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>22</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>100</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>48</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>https://cy.ncss.cn/</t>
+          <t>https://www.mcm.edu.cn/index.moma</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>https://cy.ncss.cn/</t>
+          <t>https://www.mcm.edu.cn/index.moma</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
@@ -1122,7 +1122,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>全国大学生数学建模竞赛</t>
+          <t>中国知网</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -1132,7 +1132,7 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>P1 优先关注</t>
+          <t>P2 可选参加</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -1157,25 +1157,29 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>32</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
+          <t>http://cumcm.cnki.net</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
           <t>https://www.mcm.edu.cn/index.moma</t>
         </is>
       </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>https://www.mcm.edu.cn/index.moma</t>
-        </is>
-      </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="P9" s="2" t="inlineStr"/>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="P9" s="2" t="inlineStr">
+        <is>
+          <t>标题命中误抓取关键词：中国知网。</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -1185,7 +1189,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -1195,17 +1199,17 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>2026年9月10日</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>中国知网</t>
+          <t>中国国际大学生创新大赛</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>数学建模类</t>
+          <t>创新创业类</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1220,44 +1224,40 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>24</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>64</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>20</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>40</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>http://cumcm.cnki.net</t>
+          <t>https://cy.ncss.cn/</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>https://www.mcm.edu.cn/index.moma</t>
+          <t>https://cy.ncss.cn/</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>标题命中误抓取关键词：中国知网。</t>
-        </is>
-      </c>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">

--- a/reports/schedule_report.xlsx
+++ b/reports/schedule_report.xlsx
@@ -553,7 +553,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>2025-07-25</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -563,12 +563,12 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>2025-07-25</t>
+          <t>2026.06.19</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>中国国际大学生创新大赛</t>
+          <t>挑战杯全国大学生课外学术科技作品竞赛</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -608,12 +608,12 @@
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>https://cy.ncss.cn/</t>
+          <t>https://www.tiaozhanbei.net/</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>https://cy.ncss.cn/</t>
+          <t>https://www.tiaozhanbei.net/</t>
         </is>
       </c>
       <c r="O2" s="2" t="inlineStr">
@@ -646,7 +646,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>挑战杯全国大学生课外学术科技作品竞赛</t>
+          <t>挑战杯丨第十五届“挑战杯”黑龙江省大学生创业计划竞赛终审决赛在东北林业大学举行</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -656,37 +656,37 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>P2 可选参加</t>
+          <t>P3 低优先级</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>A</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
           <t>24</t>
         </is>
       </c>
-      <c r="J3" s="2" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="K3" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="L3" s="2" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>https://www.tiaozhanbei.net/</t>
+          <t>https://www.tiaozhanbei.net/article/15846/</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
@@ -724,7 +724,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>挑战杯丨第十五届“挑战杯”黑龙江省大学生创业计划竞赛终审决赛在东北林业大学举行</t>
+          <t>挑战杯 全国大学生课外学术科技作品竞赛和创业计划大赛 官方网站 移动版</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -739,12 +739,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>S</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>24</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -764,7 +764,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>https://www.tiaozhanbei.net/article/15846/</t>
+          <t>https://www.tiaozhanbei.net/</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -774,10 +774,14 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr"/>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>标题命中误抓取关键词：官方网站 移动版。</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -802,7 +806,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>挑战杯 全国大学生课外学术科技作品竞赛和创业计划大赛 官方网站 移动版</t>
+          <t>挑战杯中国大学生创业计划竞赛</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -817,7 +821,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>A</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -837,7 +841,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>40</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -852,14 +856,10 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>标题命中误抓取关键词：官方网站 移动版。</t>
-        </is>
-      </c>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -884,7 +884,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>挑战杯中国大学生创业计划竞赛</t>
+          <t>挑战杯动态</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -919,35 +919,39 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>24</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
+          <t>https://www.tiaozhanbei.net/tzb</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
           <t>https://www.tiaozhanbei.net/</t>
         </is>
       </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>https://www.tiaozhanbei.net/</t>
-        </is>
-      </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="P6" s="2" t="inlineStr"/>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="P6" s="2" t="inlineStr">
+        <is>
+          <t>标题疑似导航/资讯/培训内容：动态。</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>正式比赛</t>
+          <t>报名/报名截止</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -957,69 +961,65 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2026.06.19</t>
+          <t>2026年9月10日</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>挑战杯动态</t>
+          <t>全国大学生数学建模竞赛</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>创新创业类</t>
+          <t>数学建模类</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>P3 低优先级</t>
+          <t>P1 优先关注</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>S</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>46</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>22</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>100</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>48</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>https://www.tiaozhanbei.net/tzb</t>
+          <t>https://www.mcm.edu.cn/index.moma</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>https://www.tiaozhanbei.net/</t>
+          <t>https://www.mcm.edu.cn/index.moma</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>标题疑似导航/资讯/培训内容：动态。</t>
-        </is>
-      </c>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -1044,7 +1044,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>全国大学生数学建模竞赛</t>
+          <t>中国知网</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1054,7 +1054,7 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>P1 优先关注</t>
+          <t>P2 可选参加</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -1079,25 +1079,29 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>32</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
+          <t>http://cumcm.cnki.net</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
           <t>https://www.mcm.edu.cn/index.moma</t>
         </is>
       </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>https://www.mcm.edu.cn/index.moma</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr"/>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>标题命中误抓取关键词：中国知网。</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -1107,7 +1111,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -1117,17 +1121,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2026年9月10日</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>中国知网</t>
+          <t>中国国际大学生创新大赛</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>数学建模类</t>
+          <t>创新创业类</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1142,54 +1146,50 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>24</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>64</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>20</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>40</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>http://cumcm.cnki.net</t>
+          <t>https://cy.ncss.cn/</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>https://www.mcm.edu.cn/index.moma</t>
+          <t>https://cy.ncss.cn/</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="P9" s="2" t="inlineStr">
-        <is>
-          <t>标题命中误抓取关键词：中国知网。</t>
-        </is>
-      </c>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="P9" s="2" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>报名/报名截止</t>
+          <t>正式比赛</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -1199,7 +1199,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
